--- a/analysis/data/annotation/[Archived] Labeling SDG 4 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 4 - Benchmarking Dataset.xlsx
@@ -18569,7 +18569,7 @@
     <row r="2">
       <c r="A2" s="17" t="str">
         <f t="shared" ref="A2:A83" si="1">LEFT(MD5(B2), 7)</f>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B2" s="48" t="s">
         <v>462</v>
@@ -18594,7 +18594,7 @@
     <row r="3">
       <c r="A3" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>203</v>
@@ -18616,7 +18616,7 @@
     <row r="4">
       <c r="A4" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>273</v>
@@ -18638,7 +18638,7 @@
     <row r="5">
       <c r="A5" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>140</v>
@@ -18660,7 +18660,7 @@
     <row r="6">
       <c r="A6" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>172</v>
@@ -18682,7 +18682,7 @@
     <row r="7">
       <c r="A7" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>259</v>
@@ -18704,7 +18704,7 @@
     <row r="8">
       <c r="A8" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>222</v>
@@ -18726,7 +18726,7 @@
     <row r="9">
       <c r="A9" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>232</v>
@@ -18748,7 +18748,7 @@
     <row r="10">
       <c r="A10" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>94</v>
@@ -18770,7 +18770,7 @@
     <row r="11">
       <c r="A11" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>138</v>
@@ -18792,7 +18792,7 @@
     <row r="12">
       <c r="A12" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>133</v>
@@ -18814,7 +18814,7 @@
     <row r="13">
       <c r="A13" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>214</v>
@@ -18836,7 +18836,7 @@
     <row r="14">
       <c r="A14" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>131</v>
@@ -18858,7 +18858,7 @@
     <row r="15">
       <c r="A15" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>136</v>
@@ -18880,7 +18880,7 @@
     <row r="16">
       <c r="A16" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>277</v>
@@ -18902,7 +18902,7 @@
     <row r="17">
       <c r="A17" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>281</v>
@@ -18924,7 +18924,7 @@
     <row r="18">
       <c r="A18" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>178</v>
@@ -18946,7 +18946,7 @@
     <row r="19">
       <c r="A19" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>265</v>
@@ -18968,7 +18968,7 @@
     <row r="20">
       <c r="A20" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>228</v>
@@ -18990,7 +18990,7 @@
     <row r="21">
       <c r="A21" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>105</v>
@@ -19012,7 +19012,7 @@
     <row r="22">
       <c r="A22" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>156</v>
@@ -19034,7 +19034,7 @@
     <row r="23">
       <c r="A23" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>174</v>
@@ -19056,7 +19056,7 @@
     <row r="24">
       <c r="A24" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>194</v>
@@ -19078,7 +19078,7 @@
     <row r="25">
       <c r="A25" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>154</v>
@@ -19100,7 +19100,7 @@
     <row r="26">
       <c r="A26" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>216</v>
@@ -19122,7 +19122,7 @@
     <row r="27">
       <c r="A27" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>248</v>
@@ -19144,7 +19144,7 @@
     <row r="28">
       <c r="A28" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>210</v>
@@ -19166,7 +19166,7 @@
     <row r="29">
       <c r="A29" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>207</v>
@@ -19188,7 +19188,7 @@
     <row r="30">
       <c r="A30" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>246</v>
@@ -19210,7 +19210,7 @@
     <row r="31">
       <c r="A31" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>148</v>
@@ -19232,7 +19232,7 @@
     <row r="32">
       <c r="A32" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>279</v>
@@ -19254,7 +19254,7 @@
     <row r="33">
       <c r="A33" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>192</v>
@@ -19276,7 +19276,7 @@
     <row r="34">
       <c r="A34" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>112</v>
@@ -19298,7 +19298,7 @@
     <row r="35">
       <c r="A35" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>218</v>
@@ -19320,7 +19320,7 @@
     <row r="36">
       <c r="A36" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>190</v>
@@ -19342,7 +19342,7 @@
     <row r="37">
       <c r="A37" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>275</v>
@@ -19364,7 +19364,7 @@
     <row r="38">
       <c r="A38" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>170</v>
@@ -19386,7 +19386,7 @@
     <row r="39">
       <c r="A39" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>129</v>
@@ -19408,7 +19408,7 @@
     <row r="40">
       <c r="A40" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>96</v>
@@ -19430,7 +19430,7 @@
     <row r="41">
       <c r="A41" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>252</v>
@@ -19452,7 +19452,7 @@
     <row r="42">
       <c r="A42" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>181</v>
@@ -19474,7 +19474,7 @@
     <row r="43">
       <c r="A43" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>166</v>
@@ -19496,7 +19496,7 @@
     <row r="44">
       <c r="A44" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>250</v>
@@ -19518,7 +19518,7 @@
     <row r="45">
       <c r="A45" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>90</v>
@@ -19540,7 +19540,7 @@
     <row r="46">
       <c r="A46" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>234</v>
@@ -19562,7 +19562,7 @@
     <row r="47">
       <c r="A47" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>263</v>
@@ -19584,7 +19584,7 @@
     <row r="48">
       <c r="A48" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>146</v>
@@ -19606,7 +19606,7 @@
     <row r="49">
       <c r="A49" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>100</v>
@@ -19628,7 +19628,7 @@
     <row r="50">
       <c r="A50" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>196</v>
@@ -19650,7 +19650,7 @@
     <row r="51">
       <c r="A51" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>102</v>
@@ -19672,7 +19672,7 @@
     <row r="52">
       <c r="A52" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>92</v>
@@ -19694,7 +19694,7 @@
     <row r="53">
       <c r="A53" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>224</v>
@@ -19716,7 +19716,7 @@
     <row r="54">
       <c r="A54" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>108</v>
@@ -19738,7 +19738,7 @@
     <row r="55">
       <c r="A55" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>230</v>
@@ -19760,7 +19760,7 @@
     <row r="56">
       <c r="A56" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>226</v>
@@ -19782,7 +19782,7 @@
     <row r="57">
       <c r="A57" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>124</v>
@@ -19804,7 +19804,7 @@
     <row r="58">
       <c r="A58" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>186</v>
@@ -19826,7 +19826,7 @@
     <row r="59">
       <c r="A59" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>142</v>
@@ -19848,7 +19848,7 @@
     <row r="60">
       <c r="A60" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>160</v>
@@ -19870,7 +19870,7 @@
     <row r="61">
       <c r="A61" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>98</v>
@@ -19892,7 +19892,7 @@
     <row r="62">
       <c r="A62" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>158</v>
@@ -19914,7 +19914,7 @@
     <row r="63">
       <c r="A63" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>122</v>
@@ -19936,7 +19936,7 @@
     <row r="64">
       <c r="A64" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>88</v>
@@ -19958,7 +19958,7 @@
     <row r="65">
       <c r="A65" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>212</v>
@@ -19980,7 +19980,7 @@
     <row r="66">
       <c r="A66" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>117</v>
@@ -20002,7 +20002,7 @@
     <row r="67">
       <c r="A67" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>257</v>
@@ -20024,7 +20024,7 @@
     <row r="68">
       <c r="A68" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>82</v>
@@ -20046,7 +20046,7 @@
     <row r="69">
       <c r="A69" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B69" s="48" t="s">
         <v>464</v>
@@ -20071,7 +20071,7 @@
     <row r="70">
       <c r="A70" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>115</v>
@@ -20093,7 +20093,7 @@
     <row r="71">
       <c r="A71" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>244</v>
@@ -20115,7 +20115,7 @@
     <row r="72">
       <c r="A72" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>162</v>
@@ -20137,7 +20137,7 @@
     <row r="73">
       <c r="A73" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>144</v>
@@ -20159,7 +20159,7 @@
     <row r="74">
       <c r="A74" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>220</v>
@@ -20181,7 +20181,7 @@
     <row r="75">
       <c r="A75" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>271</v>
@@ -20203,7 +20203,7 @@
     <row r="76">
       <c r="A76" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>79</v>
@@ -20225,7 +20225,7 @@
     <row r="77">
       <c r="A77" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>168</v>
@@ -20247,7 +20247,7 @@
     <row r="78">
       <c r="A78" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>77</v>
@@ -20269,7 +20269,7 @@
     <row r="79">
       <c r="A79" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B79" s="48" t="s">
         <v>466</v>
@@ -20294,7 +20294,7 @@
     <row r="80">
       <c r="A80" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>240</v>
@@ -20316,7 +20316,7 @@
     <row r="81">
       <c r="A81" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>242</v>
@@ -20338,7 +20338,7 @@
     <row r="82">
       <c r="A82" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>119</v>
@@ -20360,7 +20360,7 @@
     <row r="83">
       <c r="A83" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>188</v>
